--- a/data/MK_FRED_DATA_20260611.xlsx
+++ b/data/MK_FRED_DATA_20260611.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5448,25 +5448,25 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>SOFR90DAYAVG</t>
+          <t>SOFR30DAYAVG</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>SOFR 90-Day Average</t>
+          <t>SOFR 30-Day Average</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>3.668</v>
+        <v>3.593</v>
       </c>
     </row>
     <row r="220">
@@ -5485,11 +5485,11 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>3.667</v>
+        <v>3.668</v>
       </c>
     </row>
     <row r="221">
@@ -5508,11 +5508,11 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>3.666</v>
+        <v>3.667</v>
       </c>
     </row>
     <row r="222">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E222" t="n">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E223" t="n">
@@ -5577,11 +5577,11 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>3.665</v>
+        <v>3.666</v>
       </c>
     </row>
     <row r="225">
@@ -5600,11 +5600,11 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>3.664</v>
+        <v>3.665</v>
       </c>
     </row>
     <row r="226">
@@ -5623,11 +5623,11 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>3.663</v>
+        <v>3.664</v>
       </c>
     </row>
     <row r="227">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E227" t="n">
@@ -5669,11 +5669,11 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>3.662</v>
+        <v>3.663</v>
       </c>
     </row>
     <row r="229">
@@ -5692,11 +5692,11 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>3.661</v>
+        <v>3.662</v>
       </c>
     </row>
     <row r="230">
@@ -5715,11 +5715,11 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>3.657</v>
+        <v>3.661</v>
       </c>
     </row>
     <row r="231">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>3.655</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="232">
@@ -5761,11 +5761,11 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>3.653</v>
+        <v>3.655</v>
       </c>
     </row>
     <row r="233">
@@ -5784,11 +5784,11 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>3.651</v>
+        <v>3.653</v>
       </c>
     </row>
     <row r="234">
@@ -5807,11 +5807,11 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>3.649</v>
+        <v>3.651</v>
       </c>
     </row>
     <row r="235">
@@ -5830,11 +5830,11 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>3.644</v>
+        <v>3.649</v>
       </c>
     </row>
     <row r="236">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E236" t="n">
@@ -5876,11 +5876,11 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3.643</v>
+        <v>3.644</v>
       </c>
     </row>
     <row r="238">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E238" t="n">
@@ -5922,11 +5922,11 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>3.641</v>
+        <v>3.643</v>
       </c>
     </row>
     <row r="240">
@@ -5945,11 +5945,11 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>3.64</v>
+        <v>3.641</v>
       </c>
     </row>
     <row r="241">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E241" t="n">
@@ -5991,11 +5991,11 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>3.639</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="243">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E243" t="n">
@@ -6037,11 +6037,11 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>3.638</v>
+        <v>3.639</v>
       </c>
     </row>
     <row r="245">
@@ -6060,7 +6060,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E245" t="n">
@@ -6083,57 +6083,57 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>3.637</v>
+        <v>3.638</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>1.24161826</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>SOFRINDEX</t>
+          <t>SOFR90DAYAVG</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>SOFR Index</t>
+          <t>SOFR 90-Day Average</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1.24199489</v>
+        <v>3.637</v>
       </c>
     </row>
     <row r="249">
@@ -6152,11 +6152,11 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>1.24212012</v>
+        <v>1.24161826</v>
       </c>
     </row>
     <row r="250">
@@ -6175,11 +6175,11 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>1.24224503</v>
+        <v>1.24199489</v>
       </c>
     </row>
     <row r="251">
@@ -6198,11 +6198,11 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1.2423696</v>
+        <v>1.24212012</v>
       </c>
     </row>
     <row r="252">
@@ -6221,11 +6221,11 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>1.24249383</v>
+        <v>1.24224503</v>
       </c>
     </row>
     <row r="253">
@@ -6244,11 +6244,11 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>1.24286658</v>
+        <v>1.2423696</v>
       </c>
     </row>
     <row r="254">
@@ -6267,11 +6267,11 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>1.24299087</v>
+        <v>1.24249383</v>
       </c>
     </row>
     <row r="255">
@@ -6290,11 +6290,11 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E255" t="n">
-        <v>1.24311517</v>
+        <v>1.24286658</v>
       </c>
     </row>
     <row r="256">
@@ -6313,11 +6313,11 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>1.24323913</v>
+        <v>1.24299087</v>
       </c>
     </row>
     <row r="257">
@@ -6336,11 +6336,11 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1.24336207</v>
+        <v>1.24311517</v>
       </c>
     </row>
     <row r="258">
@@ -6359,11 +6359,11 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1.2437299</v>
+        <v>1.24323913</v>
       </c>
     </row>
     <row r="259">
@@ -6382,11 +6382,11 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1.24385186</v>
+        <v>1.24336207</v>
       </c>
     </row>
     <row r="260">
@@ -6405,11 +6405,11 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1.24397313</v>
+        <v>1.2437299</v>
       </c>
     </row>
     <row r="261">
@@ -6428,11 +6428,11 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1.24409407</v>
+        <v>1.24385186</v>
       </c>
     </row>
     <row r="262">
@@ -6451,11 +6451,11 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1.24421537</v>
+        <v>1.24397313</v>
       </c>
     </row>
     <row r="263">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>1.24470615</v>
+        <v>1.24409407</v>
       </c>
     </row>
     <row r="264">
@@ -6497,11 +6497,11 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>1.24483166</v>
+        <v>1.24421537</v>
       </c>
     </row>
     <row r="265">
@@ -6520,11 +6520,11 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>1.24495718</v>
+        <v>1.24470615</v>
       </c>
     </row>
     <row r="266">
@@ -6543,11 +6543,11 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>1.24508236</v>
+        <v>1.24483166</v>
       </c>
     </row>
     <row r="267">
@@ -6566,11 +6566,11 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1.245459</v>
+        <v>1.24495718</v>
       </c>
     </row>
     <row r="268">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>1.24558528</v>
+        <v>1.24508236</v>
       </c>
     </row>
     <row r="269">
@@ -6612,11 +6612,11 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1.24571087</v>
+        <v>1.245459</v>
       </c>
     </row>
     <row r="270">
@@ -6635,11 +6635,11 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>1.24583579</v>
+        <v>1.24558528</v>
       </c>
     </row>
     <row r="271">
@@ -6658,11 +6658,11 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1.24596107</v>
+        <v>1.24571087</v>
       </c>
     </row>
     <row r="272">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260604</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>1.24633797</v>
+        <v>1.24583579</v>
       </c>
     </row>
     <row r="273">
@@ -6704,11 +6704,11 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>20260609</t>
+          <t>20260605</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>1.24646364</v>
+        <v>1.24596107</v>
       </c>
     </row>
     <row r="274">
@@ -6727,80 +6727,80 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>20260610</t>
+          <t>20260608</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1.24658829</v>
+        <v>1.24633797</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>20260501</t>
+          <t>20260609</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>4.97</v>
+        <v>1.24646364</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>20260504</t>
+          <t>20260610</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>5.02</v>
+        <v>1.24658829</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>US30Y</t>
+          <t>SOFRINDEX</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>미국 국채 30년물 (CMT)</t>
+          <t>SOFR Index</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>20260505</t>
+          <t>20260611</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4.98</v>
+        <v>1.2467126</v>
       </c>
     </row>
     <row r="278">
@@ -6819,11 +6819,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>20260506</t>
+          <t>20260501</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>4.94</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="279">
@@ -6842,11 +6842,11 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>20260507</t>
+          <t>20260504</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4.97</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="280">
@@ -6865,11 +6865,11 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>20260508</t>
+          <t>20260505</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>4.95</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="281">
@@ -6888,11 +6888,11 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>20260511</t>
+          <t>20260506</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="282">
@@ -6911,11 +6911,11 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>20260512</t>
+          <t>20260507</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>5.03</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="283">
@@ -6934,11 +6934,11 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>20260513</t>
+          <t>20260508</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>5.03</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="284">
@@ -6957,11 +6957,11 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>20260514</t>
+          <t>20260511</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5.02</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="285">
@@ -6980,11 +6980,11 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>20260515</t>
+          <t>20260512</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>5.12</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="286">
@@ -7003,11 +7003,11 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>20260518</t>
+          <t>20260513</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5.14</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="287">
@@ -7026,11 +7026,11 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>20260519</t>
+          <t>20260514</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>5.18</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="288">
@@ -7049,11 +7049,11 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>20260520</t>
+          <t>20260515</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>5.11</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="289">
@@ -7072,11 +7072,11 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>20260521</t>
+          <t>20260518</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>5.1</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="290">
@@ -7095,11 +7095,11 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>20260522</t>
+          <t>20260519</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>5.07</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="291">
@@ -7118,11 +7118,11 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>20260526</t>
+          <t>20260520</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>5.03</v>
+        <v>5.11</v>
       </c>
     </row>
     <row r="292">
@@ -7141,11 +7141,11 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>20260527</t>
+          <t>20260521</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>5.01</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="293">
@@ -7164,11 +7164,11 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>20260528</t>
+          <t>20260522</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4.98</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="294">
@@ -7187,11 +7187,11 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>20260529</t>
+          <t>20260526</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>4.99</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="295">
@@ -7210,11 +7210,11 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>20260601</t>
+          <t>20260527</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>4.99</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="296">
@@ -7233,11 +7233,11 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>20260602</t>
+          <t>20260528</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="297">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>20260603</t>
+          <t>20260529</t>
         </is>
       </c>
       <c r="E297" t="n">
@@ -7279,11 +7279,11 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>20260604</t>
+          <t>20260601</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="299">
@@ -7302,11 +7302,11 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>20260605</t>
+          <t>20260602</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>5.01</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="300">
@@ -7325,11 +7325,11 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>20260608</t>
+          <t>20260603</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>5.03</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="301">
@@ -7348,10 +7348,79 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
+          <t>20260604</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>4.97</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>13</v>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>US30Y</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>미국 국채 30년물 (CMT)</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>20260605</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>5.01</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>13</v>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>US30Y</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>미국 국채 30년물 (CMT)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>20260608</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>5.03</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>13</v>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>US30Y</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>미국 국채 30년물 (CMT)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
           <t>20260609</t>
         </is>
       </c>
-      <c r="E301" t="n">
+      <c r="E304" t="n">
         <v>5.01</v>
       </c>
     </row>
